--- a/input/new_validation/10-5/instance-3.xlsx
+++ b/input/new_validation/10-5/instance-3.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,19 +511,19 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I2" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -550,19 +550,19 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>9</v>
-      </c>
-      <c r="J3" t="n">
-        <v>7</v>
-      </c>
-      <c r="K3" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -592,16 +592,16 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -628,97 +628,97 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J-0</t>
+          <t>J-1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>O-0_4</t>
+          <t>O-1_0</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J-0</t>
+          <t>J-1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>O-0_5</t>
+          <t>O-1_1</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -731,33 +731,33 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>O-1_0</t>
+          <t>O-1_2</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -770,33 +770,33 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>O-1_1</t>
+          <t>O-1_3</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -809,33 +809,33 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>O-1_2</t>
+          <t>O-1_4</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>8</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -848,111 +848,111 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>O-1_3</t>
+          <t>O-1_5</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>9</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J-1</t>
+          <t>J-2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>O-1_4</t>
+          <t>O-2_0</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J-1</t>
+          <t>J-2</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>O-1_5</t>
+          <t>O-2_1</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -965,33 +965,33 @@
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>O-2_0</t>
+          <t>O-2_2</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>12</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -1004,108 +1004,108 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>O-2_1</t>
+          <t>O-2_3</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>13</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>14</v>
       </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
       <c r="J15" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J-2</t>
+          <t>J-3</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>O-2_2</t>
+          <t>O-3_0</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>14</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J-2</t>
+          <t>J-3</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>O-2_3</t>
+          <t>O-3_1</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>15</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K17" t="n">
         <v>12</v>
@@ -1121,30 +1121,30 @@
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>O-3_0</t>
+          <t>O-3_2</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>16</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>9</v>
@@ -1160,30 +1160,30 @@
         <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>O-3_1</t>
+          <t>O-3_3</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>17</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1199,33 +1199,33 @@
         <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>O-3_2</t>
+          <t>O-3_4</t>
         </is>
       </c>
       <c r="E20" t="n">
         <v>18</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1238,69 +1238,69 @@
         <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>O-3_3</t>
+          <t>O-3_5</t>
         </is>
       </c>
       <c r="E21" t="n">
         <v>19</v>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I21" t="n">
         <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K21" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J-3</t>
+          <t>J-4</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>O-3_4</t>
+          <t>O-4_0</t>
         </is>
       </c>
       <c r="E22" t="n">
         <v>20</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1316,33 +1316,33 @@
         <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>O-4_0</t>
+          <t>O-4_1</t>
         </is>
       </c>
       <c r="E23" t="n">
         <v>21</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1355,21 +1355,21 @@
         <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>O-4_1</t>
+          <t>O-4_2</t>
         </is>
       </c>
       <c r="E24" t="n">
         <v>22</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1378,10 +1378,10 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1394,33 +1394,33 @@
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>O-4_2</t>
+          <t>O-4_3</t>
         </is>
       </c>
       <c r="E25" t="n">
         <v>23</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I25" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26">
@@ -1433,111 +1433,111 @@
         <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>O-4_3</t>
+          <t>O-4_4</t>
         </is>
       </c>
       <c r="E26" t="n">
         <v>24</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="K26" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>J-4</t>
+          <t>J-5</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>O-4_4</t>
+          <t>O-5_0</t>
         </is>
       </c>
       <c r="E27" t="n">
         <v>25</v>
       </c>
       <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>6</v>
+      </c>
+      <c r="H27" t="n">
         <v>4</v>
       </c>
-      <c r="G27" t="n">
-        <v>3</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>J-4</t>
+          <t>J-5</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>O-4_5</t>
+          <t>O-5_1</t>
         </is>
       </c>
       <c r="E28" t="n">
         <v>26</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -1550,33 +1550,33 @@
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>O-5_0</t>
+          <t>O-5_2</t>
         </is>
       </c>
       <c r="E29" t="n">
         <v>27</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H29" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I29" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="K29" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
@@ -1589,99 +1589,99 @@
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>O-5_1</t>
+          <t>O-5_3</t>
         </is>
       </c>
       <c r="E30" t="n">
         <v>28</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>15</v>
       </c>
       <c r="K30" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>J-5</t>
+          <t>J-6</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>O-5_2</t>
+          <t>O-6_0</t>
         </is>
       </c>
       <c r="E31" t="n">
         <v>29</v>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J31" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>J-5</t>
+          <t>J-6</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>O-5_3</t>
+          <t>O-6_1</t>
         </is>
       </c>
       <c r="E32" t="n">
         <v>30</v>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1690,49 +1690,49 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>J-5</t>
+          <t>J-6</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C33" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>O-5_4</t>
+          <t>O-6_2</t>
         </is>
       </c>
       <c r="E33" t="n">
         <v>31</v>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G33" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K33" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34">
@@ -1745,66 +1745,66 @@
         <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>O-6_0</t>
+          <t>O-6_3</t>
         </is>
       </c>
       <c r="E34" t="n">
         <v>32</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G34" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H34" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I34" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J34" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K34" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>J-6</t>
+          <t>J-7</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C35" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>O-6_1</t>
+          <t>O-7_0</t>
         </is>
       </c>
       <c r="E35" t="n">
         <v>33</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H35" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1816,25 +1816,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>J-6</t>
+          <t>J-7</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C36" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>O-6_2</t>
+          <t>O-7_1</t>
         </is>
       </c>
       <c r="E36" t="n">
         <v>34</v>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1843,85 +1843,85 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K36" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>J-6</t>
+          <t>J-7</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C37" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>O-6_3</t>
+          <t>O-7_2</t>
         </is>
       </c>
       <c r="E37" t="n">
         <v>35</v>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>J-6</t>
+          <t>J-7</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C38" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>O-6_4</t>
+          <t>O-7_3</t>
         </is>
       </c>
       <c r="E38" t="n">
         <v>36</v>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H38" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I38" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -1933,31 +1933,31 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>J-6</t>
+          <t>J-8</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C39" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>O-6_5</t>
+          <t>O-8_0</t>
         </is>
       </c>
       <c r="E39" t="n">
         <v>37</v>
       </c>
       <c r="F39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -1966,180 +1966,180 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>J-7</t>
+          <t>J-8</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C40" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>O-7_0</t>
+          <t>O-8_1</t>
         </is>
       </c>
       <c r="E40" t="n">
         <v>38</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H40" t="n">
         <v>6</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J40" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K40" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>J-7</t>
+          <t>J-8</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C41" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>O-7_1</t>
+          <t>O-8_2</t>
         </is>
       </c>
       <c r="E41" t="n">
         <v>39</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G41" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="K41" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>J-7</t>
+          <t>J-8</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C42" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>O-7_2</t>
+          <t>O-8_3</t>
         </is>
       </c>
       <c r="E42" t="n">
         <v>40</v>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G42" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>J-7</t>
+          <t>J-8</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C43" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>O-7_3</t>
+          <t>O-8_4</t>
         </is>
       </c>
       <c r="E43" t="n">
         <v>41</v>
       </c>
       <c r="F43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
+        <v>6</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
         <v>7</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>J-8</t>
+          <t>J-9</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C44" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>O-8_0</t>
+          <t>O-9_0</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -2149,36 +2149,36 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I44" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>J-8</t>
+          <t>J-9</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C45" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>O-8_1</t>
+          <t>O-9_1</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -2188,36 +2188,36 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>J-8</t>
+          <t>J-9</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C46" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>O-8_2</t>
+          <t>O-9_2</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -2227,16 +2227,16 @@
         <v>2</v>
       </c>
       <c r="G46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2245,18 +2245,18 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>J-8</t>
+          <t>J-9</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C47" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>O-8_3</t>
+          <t>O-9_3</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -2275,27 +2275,27 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
+        <v>7</v>
+      </c>
+      <c r="K47" t="n">
         <v>6</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>J-8</t>
+          <t>J-9</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C48" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>O-8_4</t>
+          <t>O-9_4</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -2317,7 +2317,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2330,227 +2330,32 @@
         <v>9</v>
       </c>
       <c r="C49" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>O-9_0</t>
+          <t>O-9_5</t>
         </is>
       </c>
       <c r="E49" t="n">
         <v>47</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G49" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I49" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K49" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>J-9</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>9</v>
-      </c>
-      <c r="C50" t="n">
-        <v>33</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>O-9_1</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>48</v>
-      </c>
-      <c r="F50" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" t="n">
-        <v>12</v>
-      </c>
-      <c r="H50" t="n">
-        <v>10</v>
-      </c>
-      <c r="I50" t="n">
-        <v>10</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>J-9</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>9</v>
-      </c>
-      <c r="C51" t="n">
-        <v>33</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>O-9_2</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>49</v>
-      </c>
-      <c r="F51" t="n">
-        <v>2</v>
-      </c>
-      <c r="G51" t="n">
-        <v>16</v>
-      </c>
-      <c r="H51" t="n">
-        <v>20</v>
-      </c>
-      <c r="I51" t="n">
-        <v>16</v>
-      </c>
-      <c r="J51" t="n">
-        <v>19</v>
-      </c>
-      <c r="K51" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>J-9</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>9</v>
-      </c>
-      <c r="C52" t="n">
-        <v>33</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>O-9_3</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>50</v>
-      </c>
-      <c r="F52" t="n">
-        <v>3</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
-        <v>16</v>
-      </c>
-      <c r="K52" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>J-9</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>9</v>
-      </c>
-      <c r="C53" t="n">
-        <v>33</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>O-9_4</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>51</v>
-      </c>
-      <c r="F53" t="n">
-        <v>4</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>1</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>1</v>
-      </c>
-      <c r="K53" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>J-9</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>9</v>
-      </c>
-      <c r="C54" t="n">
-        <v>33</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>O-9_5</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>52</v>
-      </c>
-      <c r="F54" t="n">
-        <v>5</v>
-      </c>
-      <c r="G54" t="n">
-        <v>15</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2603,7 +2408,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I-0</t>
+          <t>B-0</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2613,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2647,17 +2452,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M-1</t>
+          <t>I-0</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
@@ -2669,17 +2474,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B-0</t>
+          <t>M-1</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>3</v>
@@ -2713,17 +2518,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B-1</t>
+          <t>M-3</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>5</v>
@@ -2735,17 +2540,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M-3</t>
+          <t>O-0</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
         <v>6</v>
@@ -2779,17 +2584,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O-0</t>
+          <t>B-1</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>8</v>
@@ -2854,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -2876,7 +2681,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
